--- a/data/trans_bre/P1435_2011_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1435_2011_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>385,21%</t>
+          <t>383,99%</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,68</t>
+          <t>1,8; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,4</t>
+          <t>5,04; 10,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152,05; 869,43</t>
+          <t>158,1; 912,55</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>357,65%</t>
+          <t>334,63%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,84</t>
+          <t>0,82; 5,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,49</t>
+          <t>4,05; 9,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 1934,72</t>
+          <t>11,82; 2273,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127,55; 890,78</t>
+          <t>121,72; 755,21</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1090,96%</t>
+          <t>732,55%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,41</t>
+          <t>-0,21; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,91</t>
+          <t>4,77; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 1362,35</t>
+          <t>-45,93; 1467,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>277,75; 5960,53</t>
+          <t>209,33; 2949,72</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26,29</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1797,57%</t>
+          <t>539,42%</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,92</t>
+          <t>2,63; 5,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 60,05</t>
+          <t>5,67; 9,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>405,93; 8226,75</t>
+          <t>294,76; 971,3</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>265,86%</t>
+          <t>318,61%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,99</t>
+          <t>1,94; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,74</t>
+          <t>5,59; 9,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163,58; —</t>
+          <t>149,55; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94,83; 603,6</t>
+          <t>134,2; 666,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342,14%</t>
+          <t>412,97%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,43</t>
+          <t>2,32; 4,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,63</t>
+          <t>-0,18; 8,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,24</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>753,85%</t>
+          <t>423,44%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,92</t>
+          <t>2,57; 3,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 31,83</t>
+          <t>6,25; 8,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>525,88; 2102,66</t>
+          <t>494,94; 2030,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369,27; 2080,88</t>
+          <t>294,59; 604,16</t>
         </is>
       </c>
     </row>
